--- a/tracking_forms/034_property_transfer_form--tracking_forms.xlsx
+++ b/tracking_forms/034_property_transfer_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1437,46 +1437,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>property_transfer_form_14_choices</t>
+          <t>property_transfer_form_15_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>property_transfer_form_14_choices</t>
+          <t>property_transfer_form_15_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>accounting</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1505,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>property_transfer_form_15_choices</t>
+          <t>property_transfer_form_16_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>property_transfer_form_15_choices</t>
+          <t>property_transfer_form_16_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>accounting</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1573,46 +1573,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>property_transfer_form_16_choices</t>
+          <t>property_transfer_form_17_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>location_a</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Location A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>property_transfer_form_16_choices</t>
+          <t>property_transfer_form_17_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>location_b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Location B</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>location_a</t>
+          <t>location_c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Location A</t>
+          <t>Location C</t>
         </is>
       </c>
     </row>
@@ -1641,46 +1641,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>location_b</t>
+          <t>location_d</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Location B</t>
+          <t>Location D</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>property_transfer_form_17_choices</t>
+          <t>property_transfer_form_21_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>location_c</t>
+          <t>asset_a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Location C</t>
+          <t>Asset A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>property_transfer_form_17_choices</t>
+          <t>property_transfer_form_21_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>location_d</t>
+          <t>asset_b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Location D</t>
+          <t>Asset B</t>
         </is>
       </c>
     </row>
@@ -1692,44 +1692,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>asset_a</t>
+          <t>asset_c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Asset A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>property_transfer_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>asset_b</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Asset B</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>property_transfer_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>asset_c</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>Asset C</t>
         </is>
